--- a/data/onboardmeasurements/Peters_Board/Analysis/ImpliedField/Correlation_Summary.xlsx
+++ b/data/onboardmeasurements/Peters_Board/Analysis/ImpliedField/Correlation_Summary.xlsx
@@ -1,23 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+  <fileVersion appName="libxl" lastEdited="4" lowestEdited="4" rupBuild="4.6.0"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="187" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="607" uniqueCount="76">
   <si>
     <t>Board</t>
   </si>
   <si>
+    <t>Orientation</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Sensitivity_Ohms_per_G</t>
+  </si>
+  <si>
+    <t>Max_Implied_G</t>
+  </si>
+  <si>
+    <t>Max_Current_A</t>
+  </si>
+  <si>
+    <t>Correlation_G_per_A</t>
+  </si>
+  <si>
+    <t>RMSE_G</t>
+  </si>
+  <si>
     <t>Board1</t>
   </si>
   <si>
@@ -33,18 +55,12 @@
     <t>Board5</t>
   </si>
   <si>
-    <t>Orientation</t>
-  </si>
-  <si>
     <t>PointYOutToIn</t>
   </si>
   <si>
     <t>Default</t>
   </si>
   <si>
-    <t>File</t>
-  </si>
-  <si>
     <t>B1A.xlsx</t>
   </si>
   <si>
@@ -81,40 +97,46 @@
     <t>B1L.xlsx</t>
   </si>
   <si>
+    <t>B2B.xlsx</t>
+  </si>
+  <si>
+    <t>B2C.xlsx</t>
+  </si>
+  <si>
+    <t>B2D.xlsx</t>
+  </si>
+  <si>
+    <t>B2E.xlsx</t>
+  </si>
+  <si>
+    <t>B2F.xlsx</t>
+  </si>
+  <si>
+    <t>B2G.xlsx</t>
+  </si>
+  <si>
+    <t>B2H.xlsx</t>
+  </si>
+  <si>
+    <t>B2I.xlsx</t>
+  </si>
+  <si>
+    <t>B2J.xlsx</t>
+  </si>
+  <si>
+    <t>B2K.xlsx</t>
+  </si>
+  <si>
+    <t>B2L.xlsx</t>
+  </si>
+  <si>
     <t>B2A.xlsx</t>
   </si>
   <si>
-    <t>B2B.xlsx</t>
-  </si>
-  <si>
-    <t>B2C.xlsx</t>
-  </si>
-  <si>
-    <t>B2D.xlsx</t>
-  </si>
-  <si>
-    <t>B2E.xlsx</t>
-  </si>
-  <si>
-    <t>B2F.xlsx</t>
-  </si>
-  <si>
-    <t>B2G.xlsx</t>
-  </si>
-  <si>
-    <t>B2H.xlsx</t>
-  </si>
-  <si>
-    <t>B2I.xlsx</t>
-  </si>
-  <si>
-    <t>B2J.xlsx</t>
-  </si>
-  <si>
-    <t>B2K.xlsx</t>
-  </si>
-  <si>
-    <t>B2L.xlsx</t>
+    <t>B4A.xlsx</t>
+  </si>
+  <si>
+    <t>B4B.xlsx</t>
   </si>
   <si>
     <t>B3A.xlsx</t>
@@ -153,12 +175,6 @@
     <t>B3L.xlsx</t>
   </si>
   <si>
-    <t>B4A.xlsx</t>
-  </si>
-  <si>
-    <t>B4B.xlsx</t>
-  </si>
-  <si>
     <t>B4C.xlsx</t>
   </si>
   <si>
@@ -201,6 +217,9 @@
     <t>B5D.xlsx</t>
   </si>
   <si>
+    <t>B5D_X.xlsx</t>
+  </si>
+  <si>
     <t>B5E.xlsx</t>
   </si>
   <si>
@@ -223,28 +242,27 @@
   </si>
   <si>
     <t>B5L.xlsx</t>
-  </si>
-  <si>
-    <t>Sensitivity_Ohms_per_G</t>
-  </si>
-  <si>
-    <t>Max_Implied_G</t>
-  </si>
-  <si>
-    <t>Max_Current_A</t>
-  </si>
-  <si>
-    <t>Correlation_G_per_A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -255,7 +273,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -263,73 +281,379 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="true"/>
+      </left>
+      <right style="thin">
+        <color auto="true"/>
+      </right>
+      <top style="thin">
+        <color auto="true"/>
+      </top>
+      <bottom style="thin">
+        <color auto="true"/>
+      </bottom>
+      <diagonal/>
+    </border>
     <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="true"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="false"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="false">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="true"/>
     <col min="2" max="2" width="14" customWidth="true"/>
-    <col min="3" max="3" width="10.5703125" customWidth="true"/>
-    <col min="4" max="4" width="22.85546875" customWidth="true"/>
-    <col min="5" max="5" width="15" customWidth="true"/>
-    <col min="6" max="6" width="14.85546875" customWidth="true"/>
-    <col min="7" max="7" width="19.7109375" customWidth="true"/>
+    <col min="3" max="3" width="10.7109375" customWidth="true"/>
+    <col min="4" max="4" width="23" customWidth="true"/>
+    <col min="5" max="5" width="15.28515625" customWidth="true"/>
+    <col min="6" max="6" width="15" customWidth="true"/>
+    <col min="7" max="7" width="19.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>73</v>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D2" s="0">
         <v>5.6471811650833814</v>
       </c>
       <c r="E2" s="0">
-        <v>1.8805842578003806</v>
+        <v>1.214765349200426</v>
       </c>
       <c r="F2" s="0">
         <v>0.49963000000000002</v>
@@ -337,1364 +661,1675 @@
       <c r="G2" s="0">
         <v>-1.2501508601848128</v>
       </c>
+      <c r="H2">
+        <v>0.1654120968420386</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D3" s="0">
         <v>9.0210448528146099</v>
       </c>
       <c r="E3" s="0">
-        <v>1.4277725263696874</v>
+        <v>0.62187918268139797</v>
       </c>
       <c r="F3" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G3" s="0">
-        <v>-1.1889645156325035</v>
+        <v>-1.1889645156325033</v>
+      </c>
+      <c r="H3">
+        <v>0.09705823301767517</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D4" s="0">
         <v>18.050847589962718</v>
       </c>
       <c r="E4" s="0">
-        <v>1.311295765034733</v>
+        <v>0.87308919547719632</v>
       </c>
       <c r="F4" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G4" s="0">
-        <v>-1.2477590769769875</v>
+        <v>-1.2477590769769873</v>
+      </c>
+      <c r="H4">
+        <v>0.08037554489601152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D5" s="0">
         <v>28.077059763074441</v>
       </c>
       <c r="E5" s="0">
-        <v>1.1906517378278252</v>
+        <v>0.6499968356373802</v>
       </c>
       <c r="F5" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G5" s="0">
-        <v>-1.1694326122858234</v>
+        <v>-1.1694326122858238</v>
+      </c>
+      <c r="H5">
+        <v>0.04776929393366686</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6" s="0">
         <v>52.298078026188122</v>
       </c>
       <c r="E6" s="0">
-        <v>1.0969810395568929</v>
+        <v>0.54457068165554079</v>
       </c>
       <c r="F6" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G6" s="0">
-        <v>-1.0529086460798365</v>
+        <v>-1.0529086460798367</v>
+      </c>
+      <c r="H6">
+        <v>0.02249619384404992</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7" s="0">
         <v>3.8270457901679866</v>
       </c>
       <c r="E7" s="0">
-        <v>2.6103685578234828</v>
+        <v>1.0373536711268099</v>
       </c>
       <c r="F7" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.33553015651964946</v>
+        <v>-0.33553015651964929</v>
+      </c>
+      <c r="H7">
+        <v>0.3489467739561518</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D8" s="0">
         <v>21.494921029806982</v>
       </c>
       <c r="E8" s="0">
-        <v>1.1821397233684867</v>
+        <v>0.58665021297423281</v>
       </c>
       <c r="F8" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G8" s="0">
-        <v>-1.156286418740268</v>
+        <v>-1.1562864187402682</v>
+      </c>
+      <c r="H8">
+        <v>0.02468020690300423</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D9" s="0">
         <v>29.023638770722677</v>
       </c>
       <c r="E9" s="0">
-        <v>1.2310654870759426</v>
+        <v>0.59503221275678742</v>
       </c>
       <c r="F9" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G9" s="0">
-        <v>-1.2132552205934457</v>
+        <v>-1.213255220593445</v>
+      </c>
+      <c r="H9">
+        <v>0.03630937587840155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D10" s="0">
         <v>17.013887306305115</v>
       </c>
       <c r="E10" s="0">
-        <v>1.4352980926909358</v>
+        <v>0.68473475756972502</v>
       </c>
       <c r="F10" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G10" s="0">
-        <v>-1.3328868013229116</v>
+        <v>-1.3328868013229118</v>
+      </c>
+      <c r="H10">
+        <v>0.05588565985101152</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D11" s="0">
         <v>36.5103504343287</v>
       </c>
       <c r="E11" s="0">
-        <v>1.5559971165486901</v>
+        <v>1.1068094258005501</v>
       </c>
       <c r="F11" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G11" s="0">
-        <v>-1.2705483770828296</v>
+        <v>-1.2705483770828294</v>
+      </c>
+      <c r="H11">
+        <v>0.1193814473578211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D12" s="0">
         <v>51.589283233963833</v>
       </c>
       <c r="E12" s="0">
-        <v>1.0839460541910242</v>
+        <v>0.57027347843882392</v>
       </c>
       <c r="F12" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G12" s="0">
-        <v>-1.0596934676140768</v>
+        <v>-1.0596934676140759</v>
+      </c>
+      <c r="H12">
+        <v>0.01802079875922517</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D13" s="0">
         <v>2.931282006370532</v>
       </c>
       <c r="E13" s="0">
-        <v>1.9752449567834947</v>
+        <v>1.4976382314832437</v>
       </c>
       <c r="F13" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G13" s="0">
-        <v>-1.2870144353308677</v>
+        <v>-1.2870144353308679</v>
+      </c>
+      <c r="H13">
+        <v>0.1908985262782041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D14" s="0">
-        <v>125.24013166861828</v>
+        <v>26.705048719102702</v>
       </c>
       <c r="E14" s="0">
-        <v>1.1761405712167394</v>
+        <v>0.72495655048747221</v>
       </c>
       <c r="F14" s="0">
-        <v>0.49997999999999998</v>
+        <v>0.49963000000000002</v>
       </c>
       <c r="G14" s="0">
-        <v>-1.1170466589416339</v>
+        <v>-1.1385274950456705</v>
+      </c>
+      <c r="H14">
+        <v>0.05903971310875113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D15" s="0">
-        <v>26.705048719102702</v>
+        <v>113.02896184554022</v>
       </c>
       <c r="E15" s="0">
-        <v>1.3147326698148143</v>
+        <v>0.16402875596908267</v>
       </c>
       <c r="F15" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G15" s="0">
-        <v>-1.1385274950456701</v>
+        <v>-0.27125909269495524</v>
+      </c>
+      <c r="H15">
+        <v>0.01353195292532293</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D16" s="0">
-        <v>113.02896184554022</v>
+        <v>68.10490981480055</v>
       </c>
       <c r="E16" s="0">
-        <v>0.29558795776307262</v>
+        <v>0.6072983594350525</v>
       </c>
       <c r="F16" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G16" s="0">
-        <v>-0.2712590926949553</v>
+        <v>-1.1820046146433028</v>
+      </c>
+      <c r="H16">
+        <v>0.03394423913975937</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D17" s="0">
-        <v>68.10490981480055</v>
+        <v>83.46815946592136</v>
       </c>
       <c r="E17" s="0">
-        <v>1.2245813147215558</v>
+        <v>0.57471016860730595</v>
       </c>
       <c r="F17" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G17" s="0">
-        <v>-1.1820046146433025</v>
+        <v>-1.084484672985766</v>
+      </c>
+      <c r="H17">
+        <v>0.02627866298097563</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D18" s="0">
-        <v>83.46815946592136</v>
+        <v>22.172505307723824</v>
       </c>
       <c r="E18" s="0">
-        <v>1.1472638262628991</v>
+        <v>0.70763316017954425</v>
       </c>
       <c r="F18" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G18" s="0">
-        <v>-1.0844846729857658</v>
+        <v>-1.0030575782141413</v>
+      </c>
+      <c r="H18">
+        <v>0.2490932135888003</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D19" s="0">
-        <v>22.172505307723824</v>
+        <v>12.427231500062058</v>
       </c>
       <c r="E19" s="0">
-        <v>2.8350427309674928</v>
+        <v>0.94148081171143705</v>
       </c>
       <c r="F19" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G19" s="0">
-        <v>-1.0030575782141413</v>
+        <v>-1.2450152596485304</v>
+      </c>
+      <c r="H19">
+        <v>0.08062640248238774</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D20" s="0">
-        <v>12.427231500062058</v>
+        <v>31.624233919590871</v>
       </c>
       <c r="E20" s="0">
-        <v>1.6673061896286148</v>
+        <v>0.71559045691153766</v>
       </c>
       <c r="F20" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G20" s="0">
-        <v>-1.2450152596485302</v>
+        <v>-1.2229012030941111</v>
+      </c>
+      <c r="H20">
+        <v>0.04903073204720567</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D21" s="0">
-        <v>31.624233919590871</v>
+        <v>146.46140313902819</v>
       </c>
       <c r="E21" s="0">
-        <v>1.2803472205192248</v>
+        <v>0.62398692106785048</v>
       </c>
       <c r="F21" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G21" s="0">
-        <v>-1.2229012030941118</v>
+        <v>-1.2383302168756785</v>
+      </c>
+      <c r="H21">
+        <v>0.0144425677746405</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D22" s="0">
-        <v>146.46140313902819</v>
+        <v>97.865660258213907</v>
       </c>
       <c r="E22" s="0">
-        <v>1.24749590051769</v>
+        <v>0.65497948750236812</v>
       </c>
       <c r="F22" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G22" s="0">
-        <v>-1.238330216875678</v>
+        <v>-1.1912337679058096</v>
+      </c>
+      <c r="H22">
+        <v>0.02341128697454981</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D23" s="0">
-        <v>97.865660258213907</v>
+        <v>78.639759104510361</v>
       </c>
       <c r="E23" s="0">
-        <v>1.2200397941931571</v>
+        <v>0.54349098327218326</v>
       </c>
       <c r="F23" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G23" s="0">
-        <v>-1.1912337679058091</v>
+        <v>-1.0693951488132296</v>
+      </c>
+      <c r="H23">
+        <v>0.01208880711305554</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D24" s="0">
-        <v>78.639759104510361</v>
+        <v>10.246637752907171</v>
       </c>
       <c r="E24" s="0">
-        <v>1.0775719682378544</v>
+        <v>0.58165421123706251</v>
       </c>
       <c r="F24" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G24" s="0">
-        <v>-1.0693951488132285</v>
+        <v>-1.0111696172658142</v>
+      </c>
+      <c r="H24">
+        <v>0.1720747126153388</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D25" s="0">
-        <v>10.246637752907171</v>
+        <v>125.24013166861828</v>
       </c>
       <c r="E25" s="0">
-        <v>1.3741092775537005</v>
+        <v>0.60922963736476998</v>
       </c>
       <c r="F25" s="0">
-        <v>0.49963000000000002</v>
+        <v>0.49997999999999998</v>
       </c>
       <c r="G25" s="0">
-        <v>-1.0111696172658144</v>
+        <v>-1.1170466589416339</v>
+      </c>
+      <c r="H25">
+        <v>0.05242003468507923</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D26" s="0">
-        <v>73.577437891801424</v>
+        <v>58.629519152132581</v>
       </c>
       <c r="E26" s="0">
-        <v>1.1079483376396242</v>
+        <v>0.59782172030193104</v>
       </c>
       <c r="F26" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G26" s="0">
-        <v>-0.99659111749404539</v>
+        <v>-1.1269150435450535</v>
+      </c>
+      <c r="H26">
+        <v>0.05321003216062429</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D27" s="0">
-        <v>50.316769174096926</v>
+        <v>72.638907860450047</v>
       </c>
       <c r="E27" s="0">
-        <v>1.6461708762223675</v>
+        <v>0.71724646659174696</v>
       </c>
       <c r="F27" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G27" s="0">
-        <v>-1.1023295890374962</v>
+        <v>-1.175470651749928</v>
+      </c>
+      <c r="H27">
+        <v>0.0489767771866955</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D28" s="0">
-        <v>54.195115066205972</v>
+        <v>73.577437891801424</v>
       </c>
       <c r="E28" s="0">
-        <v>1.2502971885421337</v>
+        <v>0.61295964214365795</v>
       </c>
       <c r="F28" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G28" s="0">
-        <v>-1.1964155275590849</v>
+        <v>-0.99659111749404539</v>
+      </c>
+      <c r="H28">
+        <v>0.05743760351832346</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D29" s="0">
-        <v>75.345206432977364</v>
+        <v>50.316769174096926</v>
       </c>
       <c r="E29" s="0">
-        <v>1.2819660940993938</v>
+        <v>0.56899519722628333</v>
       </c>
       <c r="F29" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G29" s="0">
-        <v>-1.1475026770084069</v>
+        <v>-1.1023295890374967</v>
+      </c>
+      <c r="H29">
+        <v>0.1089673922558824</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D30" s="0">
-        <v>85.273182305018693</v>
+        <v>54.195115066205972</v>
       </c>
       <c r="E30" s="0">
-        <v>1.1208682192499395</v>
+        <v>0.5911971948182565</v>
       </c>
       <c r="F30" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G30" s="0">
-        <v>-1.1116267391397157</v>
+        <v>-1.1964155275590835</v>
+      </c>
+      <c r="H30">
+        <v>0.02834230787526099</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D31" s="0">
-        <v>20.506561165485355</v>
+        <v>75.345206432977364</v>
       </c>
       <c r="E31" s="0">
-        <v>1.1235428414388089</v>
+        <v>0.6245918251197502</v>
       </c>
       <c r="F31" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G31" s="0">
-        <v>-0.96703398480208913</v>
+        <v>-1.1475026770084065</v>
+      </c>
+      <c r="H31">
+        <v>0.03735176102394584</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D32" s="0">
-        <v>25.145292878613631</v>
+        <v>85.273182305018693</v>
       </c>
       <c r="E32" s="0">
-        <v>1.1620465166605047</v>
+        <v>0.57286474691731437</v>
       </c>
       <c r="F32" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G32" s="0">
-        <v>-1.0648047082047316</v>
+        <v>-1.1116267391397157</v>
+      </c>
+      <c r="H32">
+        <v>0.01326416722233131</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D33" s="0">
-        <v>37.959457094638872</v>
+        <v>20.506561165485355</v>
       </c>
       <c r="E33" s="0">
-        <v>1.1583411187988562</v>
+        <v>0.66125177647216127</v>
       </c>
       <c r="F33" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G33" s="0">
-        <v>-1.0602309233410907</v>
+        <v>-0.96703398480208924</v>
+      </c>
+      <c r="H33">
+        <v>0.1219832709188648</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D34" s="0">
-        <v>59.550631194164545</v>
+        <v>25.145292878613631</v>
       </c>
       <c r="E34" s="0">
-        <v>1.2787437928526311</v>
+        <v>0.54721971489562882</v>
       </c>
       <c r="F34" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G34" s="0">
-        <v>-1.2062246655230169</v>
+        <v>-1.0648047082047316</v>
+      </c>
+      <c r="H34">
+        <v>0.04312376780458648</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D35" s="0">
-        <v>72.57839507479575</v>
+        <v>37.959457094638872</v>
       </c>
       <c r="E35" s="0">
-        <v>1.2545055578339976</v>
+        <v>0.46312569634945128</v>
       </c>
       <c r="F35" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G35" s="0">
-        <v>-1.2070623513433487</v>
+        <v>-1.0602309233410912</v>
+      </c>
+      <c r="H35">
+        <v>0.04013415624161748</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D36" s="0">
-        <v>95.35641614153549</v>
+        <v>59.550631194164545</v>
       </c>
       <c r="E36" s="0">
-        <v>1.1336415982700947</v>
+        <v>0.63223511229018781</v>
       </c>
       <c r="F36" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G36" s="0">
-        <v>-1.1099774655552124</v>
+        <v>-1.2062246655230176</v>
+      </c>
+      <c r="H36">
+        <v>0.02908355500126322</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D37" s="0">
-        <v>79.032219430701588</v>
+        <v>72.57839507479575</v>
       </c>
       <c r="E37" s="0">
-        <v>1.0367923435561668</v>
+        <v>0.62346377256437757</v>
       </c>
       <c r="F37" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G37" s="0">
-        <v>-1.001349158512697</v>
+        <v>-1.2070623513433476</v>
+      </c>
+      <c r="H37">
+        <v>0.02414242681753815</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D38" s="0">
-        <v>58.629519152132581</v>
+        <v>95.35641614153549</v>
       </c>
       <c r="E38" s="0">
-        <v>1.162895431959432</v>
+        <v>0.55622895811514916</v>
       </c>
       <c r="F38" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G38" s="0">
-        <v>-1.1269150435450528</v>
+        <v>-1.109977465555213</v>
+      </c>
+      <c r="H38">
+        <v>0.01192889538873222</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D39" s="0">
-        <v>72.638907860450047</v>
+        <v>79.032219430701588</v>
       </c>
       <c r="E39" s="0">
-        <v>1.2421717597040547</v>
+        <v>0.5300369937950451</v>
       </c>
       <c r="F39" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G39" s="0">
-        <v>-1.1754706517499285</v>
+        <v>-1.0013491585126972</v>
+      </c>
+      <c r="H39">
+        <v>0.02130834902060431</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D40" s="0">
-        <v>83.057774310989032</v>
+        <v>58.629519152132581</v>
       </c>
       <c r="E40" s="0">
-        <v>1.2945206019778759</v>
+        <v>0.59782172030193104</v>
       </c>
       <c r="F40" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G40" s="0">
-        <v>-1.2372589705037929</v>
+        <v>-1.1269150435450535</v>
+      </c>
+      <c r="H40">
+        <v>0.05321003216062429</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D41" s="0">
-        <v>99.275685744455686</v>
+        <v>72.638907860450047</v>
       </c>
       <c r="E41" s="0">
-        <v>1.1762195257010437</v>
+        <v>0.71724646659174696</v>
       </c>
       <c r="F41" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G41" s="0">
-        <v>-1.1596404174790787</v>
+        <v>-1.175470651749928</v>
+      </c>
+      <c r="H41">
+        <v>0.0489767771866955</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D42" s="0">
-        <v>88.375529301604587</v>
+        <v>83.057774310989032</v>
       </c>
       <c r="E42" s="0">
-        <v>1.0481408228274742</v>
+        <v>0.635340886964055</v>
       </c>
       <c r="F42" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G42" s="0">
-        <v>-1.0316473996838393</v>
+        <v>-1.2372589705037926</v>
+      </c>
+      <c r="H42">
+        <v>0.04978529067558385</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D43" s="0">
-        <v>47.352224530740223</v>
+        <v>99.275685744455686</v>
       </c>
       <c r="E43" s="0">
-        <v>1.0749231003276478</v>
+        <v>0.57224485103262435</v>
       </c>
       <c r="F43" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G43" s="0">
-        <v>-0.9249986793065148</v>
+        <v>-1.1596404174790782</v>
+      </c>
+      <c r="H43">
+        <v>0.01807839158434939</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D44" s="0">
-        <v>49.576942184101256</v>
+        <v>88.375529301604587</v>
       </c>
       <c r="E44" s="0">
-        <v>1.2741810449991031</v>
+        <v>0.51360371313980124</v>
       </c>
       <c r="F44" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G44" s="0">
-        <v>-1.0345908580540746</v>
+        <v>-1.0316473996838389</v>
+      </c>
+      <c r="H44">
+        <v>0.00943203805553001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D45" s="0">
-        <v>76.638085372631863</v>
+        <v>47.352224530740223</v>
       </c>
       <c r="E45" s="0">
-        <v>1.2929602757975791</v>
+        <v>0.44982047223938398</v>
       </c>
       <c r="F45" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G45" s="0">
-        <v>-1.2485387591333057</v>
+        <v>-0.92499867930651436</v>
+      </c>
+      <c r="H45">
+        <v>0.08443146555095914</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D46" s="0">
-        <v>84.75048372380536</v>
+        <v>49.576942184101256</v>
       </c>
       <c r="E46" s="0">
-        <v>1.295095852876702</v>
+        <v>0.6821719636197755</v>
       </c>
       <c r="F46" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G46" s="0">
-        <v>-1.183416319241446</v>
+        <v>-1.0345908580540746</v>
+      </c>
+      <c r="H46">
+        <v>0.06277177630658007</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D47" s="0">
-        <v>83.134288073619331</v>
+        <v>76.638085372631863</v>
       </c>
       <c r="E47" s="0">
-        <v>1.1617348537883141</v>
+        <v>0.71139564271342159</v>
       </c>
       <c r="F47" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G47" s="0">
-        <v>-1.1392480998525256</v>
+        <v>-1.2485387591333048</v>
+      </c>
+      <c r="H47">
+        <v>0.03098870296615477</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D48" s="0">
-        <v>2269.2076519151688</v>
+        <v>84.75048372380536</v>
       </c>
       <c r="E48" s="0">
-        <v>3675.5604948540877</v>
+        <v>0.74713437868226806</v>
       </c>
       <c r="F48" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G48" s="0">
-        <v>-121.56768029662031</v>
+        <v>-1.1834163192414453</v>
+      </c>
+      <c r="H48">
+        <v>0.04844182101246118</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D49" s="0">
-        <v>51.784904986979562</v>
+        <v>83.134288073619331</v>
       </c>
       <c r="E49" s="0">
-        <v>1.3478831334643355</v>
+        <v>0.60263943026299704</v>
       </c>
       <c r="F49" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G49" s="0">
-        <v>-0.85196735207757524</v>
+        <v>-1.1392480998525256</v>
+      </c>
+      <c r="H49">
+        <v>0.01889493132586368</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D50" s="0">
-        <v>7.4142708769332089</v>
+        <v>2269.2076519151688</v>
       </c>
       <c r="E50" s="0">
-        <v>1.6346853522319458</v>
+        <v>3636.1767038094149</v>
       </c>
       <c r="F50" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G50" s="0">
-        <v>-1.1413130059961121</v>
+        <v>-121.56768029662025</v>
+      </c>
+      <c r="H50">
+        <v>255.2353512560123</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D51" s="0">
-        <v>13.48998729811724</v>
+        <v>51.784904986979562</v>
       </c>
       <c r="E51" s="0">
-        <v>1.218681651560696</v>
+        <v>0.88828974411686035</v>
       </c>
       <c r="F51" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G51" s="0">
-        <v>-1.1288539220642178</v>
+        <v>-0.85196735207757446</v>
+      </c>
+      <c r="H51">
+        <v>0.1729359348681366</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D52" s="0">
-        <v>24.903241735996083</v>
+        <v>58.629519152132581</v>
       </c>
       <c r="E52" s="0">
-        <v>1.260880022483476</v>
+        <v>0.59782172030193104</v>
       </c>
       <c r="F52" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G52" s="0">
-        <v>-1.1601417802533474</v>
+        <v>-1.1269150435450535</v>
+      </c>
+      <c r="H52">
+        <v>0.05321003216062429</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D53" s="0">
-        <v>35.813386667504801</v>
+        <v>72.638907860450047</v>
       </c>
       <c r="E53" s="0">
-        <v>1.1973176510252925</v>
+        <v>0.71724646659174696</v>
       </c>
       <c r="F53" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G53" s="0">
-        <v>-1.1360765656941463</v>
+        <v>-1.175470651749928</v>
+      </c>
+      <c r="H53">
+        <v>0.0489767771866955</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D54" s="0">
-        <v>62.92001142089412</v>
+        <v>7.4142708769332089</v>
       </c>
       <c r="E54" s="0">
-        <v>1.0797836565147412</v>
+        <v>0.98054146128138098</v>
       </c>
       <c r="F54" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G54" s="0">
-        <v>-1.0715663031221223</v>
+        <v>-1.1413130059961114</v>
+      </c>
+      <c r="H54">
+        <v>0.1672137576914152</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D55" s="0">
-        <v>74.75504147874878</v>
+        <v>13.48998729811724</v>
       </c>
       <c r="E55" s="0">
-        <v>1.068958004962383</v>
+        <v>0.62268405554198114</v>
       </c>
       <c r="F55" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G55" s="0">
-        <v>-0.97416911250688876</v>
+        <v>-1.1288539220642178</v>
+      </c>
+      <c r="H55">
+        <v>0.06368918367593454</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D56" s="0">
-        <v>6.356654786633988</v>
+        <v>24.903241735996083</v>
       </c>
       <c r="E56" s="0">
-        <v>1.5070819985597057</v>
+        <v>0.6083545331407918</v>
       </c>
       <c r="F56" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G56" s="0">
-        <v>-1.0473833351419979</v>
+        <v>-1.1601417802533474</v>
+      </c>
+      <c r="H56">
+        <v>0.04290000302312324</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D57" s="0">
-        <v>12.336462321580468</v>
+        <v>35.813386667504801</v>
       </c>
       <c r="E57" s="0">
-        <v>1.3083167264058619</v>
+        <v>0.62797747135163329</v>
       </c>
       <c r="F57" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G57" s="0">
-        <v>-1.1579163921851643</v>
+        <v>-1.1360765656941458</v>
+      </c>
+      <c r="H57">
+        <v>0.03206734117157507</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D58" s="0">
-        <v>21.989221389635926</v>
+        <v>35.813386667504801</v>
       </c>
       <c r="E58" s="0">
-        <v>1.3033658396614112</v>
+        <v>239593.9283727571</v>
       </c>
       <c r="F58" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G58" s="0">
-        <v>-1.2477824177519548</v>
+        <v>-6988.9221308028855</v>
+      </c>
+      <c r="H58">
+        <v>16799.31534518912</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D59" s="0">
-        <v>36.097622203967944</v>
+        <v>62.92001142089412</v>
       </c>
       <c r="E59" s="0">
-        <v>1.1920452753607929</v>
+        <v>0.49189437988117385</v>
       </c>
       <c r="F59" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G59" s="0">
-        <v>-1.179786253518166</v>
+        <v>-1.0715663031221219</v>
+      </c>
+      <c r="H59">
+        <v>0.01359098568294229</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D60" s="0">
-        <v>58.315996979022707</v>
+        <v>74.75504147874878</v>
       </c>
       <c r="E60" s="0">
-        <v>1.1242198263982481</v>
+        <v>0.52464688968369511</v>
       </c>
       <c r="F60" s="0">
         <v>0.49963000000000002</v>
       </c>
       <c r="G60" s="0">
-        <v>-1.1094377641218587</v>
+        <v>-0.97416911250688898</v>
+      </c>
+      <c r="H60">
+        <v>0.04179688413380851</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D61" s="0">
+        <v>6.356654786633988</v>
+      </c>
+      <c r="E61" s="0">
+        <v>0.95333161913085374</v>
+      </c>
+      <c r="F61" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G61" s="0">
+        <v>-1.0473833351419974</v>
+      </c>
+      <c r="H61">
+        <v>0.1358014739224134</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="D62" s="0">
+        <v>12.336462321580468</v>
+      </c>
+      <c r="E62" s="0">
+        <v>0.73197645845376935</v>
+      </c>
+      <c r="F62" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G62" s="0">
+        <v>-1.157916392185165</v>
+      </c>
+      <c r="H62">
+        <v>0.06890293652652933</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" s="0">
+        <v>21.989221389635926</v>
+      </c>
+      <c r="E63" s="0">
+        <v>0.63303742107754213</v>
+      </c>
+      <c r="F63" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G63" s="0">
+        <v>-1.2477824177519539</v>
+      </c>
+      <c r="H63">
+        <v>0.04550107762404755</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D64" s="0">
+        <v>36.097622203967944</v>
+      </c>
+      <c r="E64" s="0">
+        <v>0.68176235711435274</v>
+      </c>
+      <c r="F64" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G64" s="0">
+        <v>-1.1797862535181651</v>
+      </c>
+      <c r="H64">
+        <v>0.03241921170643409</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="D65" s="0">
+        <v>58.315996979022707</v>
+      </c>
+      <c r="E65" s="0">
+        <v>0.5535359364877277</v>
+      </c>
+      <c r="F65" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G65" s="0">
+        <v>-1.1094377641218596</v>
+      </c>
+      <c r="H65">
+        <v>0.02200307295368991</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" s="0">
         <v>61.461304174398421</v>
       </c>
-      <c r="E61" s="0">
-        <v>1.0974384762259535</v>
-      </c>
-      <c r="F61" s="0">
-        <v>0.49963000000000002</v>
-      </c>
-      <c r="G61" s="0">
+      <c r="E66" s="0">
+        <v>0.5906155179688426</v>
+      </c>
+      <c r="F66" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G66" s="0">
         <v>-0.99791097125424666</v>
       </c>
+      <c r="H66">
+        <v>0.04366557286781612</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>